--- a/N100 Financial Intelligence Platform/data/raw/companies.xlsx
+++ b/N100 Financial Intelligence Platform/data/raw/companies.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="195">
   <si>
     <t>company_id</t>
   </si>
@@ -25,56 +25,587 @@
     <t>company_name</t>
   </si>
   <si>
-    <t>bse_code</t>
-  </si>
-  <si>
-    <t>nse_code</t>
-  </si>
-  <si>
-    <t>website</t>
-  </si>
-  <si>
-    <t>TCS</t>
-  </si>
-  <si>
-    <t>INFY</t>
-  </si>
-  <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t>Infosys</t>
-  </si>
-  <si>
-    <t>Reliance Industries</t>
-  </si>
-  <si>
-    <t>532540</t>
-  </si>
-  <si>
-    <t>500209</t>
-  </si>
-  <si>
-    <t>500325</t>
-  </si>
-  <si>
-    <t>https://www.tcs.com</t>
-  </si>
-  <si>
-    <t>https://www.infosys.com</t>
-  </si>
-  <si>
-    <t>https://www.ril.com</t>
+    <t>broad_sector</t>
+  </si>
+  <si>
+    <t>equity_capital</t>
+  </si>
+  <si>
+    <t>reserves</t>
+  </si>
+  <si>
+    <t>roce_percentage</t>
+  </si>
+  <si>
+    <t>roe_percentage</t>
+  </si>
+  <si>
+    <t>DEMO001</t>
+  </si>
+  <si>
+    <t>DEMO002</t>
+  </si>
+  <si>
+    <t>DEMO003</t>
+  </si>
+  <si>
+    <t>DEMO004</t>
+  </si>
+  <si>
+    <t>DEMO005</t>
+  </si>
+  <si>
+    <t>DEMO006</t>
+  </si>
+  <si>
+    <t>DEMO007</t>
+  </si>
+  <si>
+    <t>DEMO008</t>
+  </si>
+  <si>
+    <t>DEMO009</t>
+  </si>
+  <si>
+    <t>DEMO010</t>
+  </si>
+  <si>
+    <t>DEMO011</t>
+  </si>
+  <si>
+    <t>DEMO012</t>
+  </si>
+  <si>
+    <t>DEMO013</t>
+  </si>
+  <si>
+    <t>DEMO014</t>
+  </si>
+  <si>
+    <t>DEMO015</t>
+  </si>
+  <si>
+    <t>DEMO016</t>
+  </si>
+  <si>
+    <t>DEMO017</t>
+  </si>
+  <si>
+    <t>DEMO018</t>
+  </si>
+  <si>
+    <t>DEMO019</t>
+  </si>
+  <si>
+    <t>DEMO020</t>
+  </si>
+  <si>
+    <t>DEMO021</t>
+  </si>
+  <si>
+    <t>DEMO022</t>
+  </si>
+  <si>
+    <t>DEMO023</t>
+  </si>
+  <si>
+    <t>DEMO024</t>
+  </si>
+  <si>
+    <t>DEMO025</t>
+  </si>
+  <si>
+    <t>DEMO026</t>
+  </si>
+  <si>
+    <t>DEMO027</t>
+  </si>
+  <si>
+    <t>DEMO028</t>
+  </si>
+  <si>
+    <t>DEMO029</t>
+  </si>
+  <si>
+    <t>DEMO030</t>
+  </si>
+  <si>
+    <t>DEMO031</t>
+  </si>
+  <si>
+    <t>DEMO032</t>
+  </si>
+  <si>
+    <t>DEMO033</t>
+  </si>
+  <si>
+    <t>DEMO034</t>
+  </si>
+  <si>
+    <t>DEMO035</t>
+  </si>
+  <si>
+    <t>DEMO036</t>
+  </si>
+  <si>
+    <t>DEMO037</t>
+  </si>
+  <si>
+    <t>DEMO038</t>
+  </si>
+  <si>
+    <t>DEMO039</t>
+  </si>
+  <si>
+    <t>DEMO040</t>
+  </si>
+  <si>
+    <t>DEMO041</t>
+  </si>
+  <si>
+    <t>DEMO042</t>
+  </si>
+  <si>
+    <t>DEMO043</t>
+  </si>
+  <si>
+    <t>DEMO044</t>
+  </si>
+  <si>
+    <t>DEMO045</t>
+  </si>
+  <si>
+    <t>DEMO046</t>
+  </si>
+  <si>
+    <t>DEMO047</t>
+  </si>
+  <si>
+    <t>DEMO048</t>
+  </si>
+  <si>
+    <t>DEMO049</t>
+  </si>
+  <si>
+    <t>DEMO050</t>
+  </si>
+  <si>
+    <t>DEMO051</t>
+  </si>
+  <si>
+    <t>DEMO052</t>
+  </si>
+  <si>
+    <t>DEMO053</t>
+  </si>
+  <si>
+    <t>DEMO054</t>
+  </si>
+  <si>
+    <t>DEMO055</t>
+  </si>
+  <si>
+    <t>DEMO056</t>
+  </si>
+  <si>
+    <t>DEMO057</t>
+  </si>
+  <si>
+    <t>DEMO058</t>
+  </si>
+  <si>
+    <t>DEMO059</t>
+  </si>
+  <si>
+    <t>DEMO060</t>
+  </si>
+  <si>
+    <t>DEMO061</t>
+  </si>
+  <si>
+    <t>DEMO062</t>
+  </si>
+  <si>
+    <t>DEMO063</t>
+  </si>
+  <si>
+    <t>DEMO064</t>
+  </si>
+  <si>
+    <t>DEMO065</t>
+  </si>
+  <si>
+    <t>DEMO066</t>
+  </si>
+  <si>
+    <t>DEMO067</t>
+  </si>
+  <si>
+    <t>DEMO068</t>
+  </si>
+  <si>
+    <t>DEMO069</t>
+  </si>
+  <si>
+    <t>DEMO070</t>
+  </si>
+  <si>
+    <t>DEMO071</t>
+  </si>
+  <si>
+    <t>DEMO072</t>
+  </si>
+  <si>
+    <t>DEMO073</t>
+  </si>
+  <si>
+    <t>DEMO074</t>
+  </si>
+  <si>
+    <t>DEMO075</t>
+  </si>
+  <si>
+    <t>DEMO076</t>
+  </si>
+  <si>
+    <t>DEMO077</t>
+  </si>
+  <si>
+    <t>DEMO078</t>
+  </si>
+  <si>
+    <t>DEMO079</t>
+  </si>
+  <si>
+    <t>DEMO080</t>
+  </si>
+  <si>
+    <t>DEMO081</t>
+  </si>
+  <si>
+    <t>DEMO082</t>
+  </si>
+  <si>
+    <t>DEMO083</t>
+  </si>
+  <si>
+    <t>DEMO084</t>
+  </si>
+  <si>
+    <t>DEMO085</t>
+  </si>
+  <si>
+    <t>DEMO086</t>
+  </si>
+  <si>
+    <t>DEMO087</t>
+  </si>
+  <si>
+    <t>DEMO088</t>
+  </si>
+  <si>
+    <t>DEMO089</t>
+  </si>
+  <si>
+    <t>DEMO090</t>
+  </si>
+  <si>
+    <t>DEMO091</t>
+  </si>
+  <si>
+    <t>DEMO092</t>
+  </si>
+  <si>
+    <t>Demo Company 001</t>
+  </si>
+  <si>
+    <t>Demo Company 002</t>
+  </si>
+  <si>
+    <t>Demo Company 003</t>
+  </si>
+  <si>
+    <t>Demo Company 004</t>
+  </si>
+  <si>
+    <t>Demo Company 005</t>
+  </si>
+  <si>
+    <t>Demo Company 006</t>
+  </si>
+  <si>
+    <t>Demo Company 007</t>
+  </si>
+  <si>
+    <t>Demo Company 008</t>
+  </si>
+  <si>
+    <t>Demo Company 009</t>
+  </si>
+  <si>
+    <t>Demo Company 010</t>
+  </si>
+  <si>
+    <t>Demo Company 011</t>
+  </si>
+  <si>
+    <t>Demo Company 012</t>
+  </si>
+  <si>
+    <t>Demo Company 013</t>
+  </si>
+  <si>
+    <t>Demo Company 014</t>
+  </si>
+  <si>
+    <t>Demo Company 015</t>
+  </si>
+  <si>
+    <t>Demo Company 016</t>
+  </si>
+  <si>
+    <t>Demo Company 017</t>
+  </si>
+  <si>
+    <t>Demo Company 018</t>
+  </si>
+  <si>
+    <t>Demo Company 019</t>
+  </si>
+  <si>
+    <t>Demo Company 020</t>
+  </si>
+  <si>
+    <t>Demo Company 021</t>
+  </si>
+  <si>
+    <t>Demo Company 022</t>
+  </si>
+  <si>
+    <t>Demo Company 023</t>
+  </si>
+  <si>
+    <t>Demo Company 024</t>
+  </si>
+  <si>
+    <t>Demo Company 025</t>
+  </si>
+  <si>
+    <t>Demo Company 026</t>
+  </si>
+  <si>
+    <t>Demo Company 027</t>
+  </si>
+  <si>
+    <t>Demo Company 028</t>
+  </si>
+  <si>
+    <t>Demo Company 029</t>
+  </si>
+  <si>
+    <t>Demo Company 030</t>
+  </si>
+  <si>
+    <t>Demo Company 031</t>
+  </si>
+  <si>
+    <t>Demo Company 032</t>
+  </si>
+  <si>
+    <t>Demo Company 033</t>
+  </si>
+  <si>
+    <t>Demo Company 034</t>
+  </si>
+  <si>
+    <t>Demo Company 035</t>
+  </si>
+  <si>
+    <t>Demo Company 036</t>
+  </si>
+  <si>
+    <t>Demo Company 037</t>
+  </si>
+  <si>
+    <t>Demo Company 038</t>
+  </si>
+  <si>
+    <t>Demo Company 039</t>
+  </si>
+  <si>
+    <t>Demo Company 040</t>
+  </si>
+  <si>
+    <t>Demo Company 041</t>
+  </si>
+  <si>
+    <t>Demo Company 042</t>
+  </si>
+  <si>
+    <t>Demo Company 043</t>
+  </si>
+  <si>
+    <t>Demo Company 044</t>
+  </si>
+  <si>
+    <t>Demo Company 045</t>
+  </si>
+  <si>
+    <t>Demo Company 046</t>
+  </si>
+  <si>
+    <t>Demo Company 047</t>
+  </si>
+  <si>
+    <t>Demo Company 048</t>
+  </si>
+  <si>
+    <t>Demo Company 049</t>
+  </si>
+  <si>
+    <t>Demo Company 050</t>
+  </si>
+  <si>
+    <t>Demo Company 051</t>
+  </si>
+  <si>
+    <t>Demo Company 052</t>
+  </si>
+  <si>
+    <t>Demo Company 053</t>
+  </si>
+  <si>
+    <t>Demo Company 054</t>
+  </si>
+  <si>
+    <t>Demo Company 055</t>
+  </si>
+  <si>
+    <t>Demo Company 056</t>
+  </si>
+  <si>
+    <t>Demo Company 057</t>
+  </si>
+  <si>
+    <t>Demo Company 058</t>
+  </si>
+  <si>
+    <t>Demo Company 059</t>
+  </si>
+  <si>
+    <t>Demo Company 060</t>
+  </si>
+  <si>
+    <t>Demo Company 061</t>
+  </si>
+  <si>
+    <t>Demo Company 062</t>
+  </si>
+  <si>
+    <t>Demo Company 063</t>
+  </si>
+  <si>
+    <t>Demo Company 064</t>
+  </si>
+  <si>
+    <t>Demo Company 065</t>
+  </si>
+  <si>
+    <t>Demo Company 066</t>
+  </si>
+  <si>
+    <t>Demo Company 067</t>
+  </si>
+  <si>
+    <t>Demo Company 068</t>
+  </si>
+  <si>
+    <t>Demo Company 069</t>
+  </si>
+  <si>
+    <t>Demo Company 070</t>
+  </si>
+  <si>
+    <t>Demo Company 071</t>
+  </si>
+  <si>
+    <t>Demo Company 072</t>
+  </si>
+  <si>
+    <t>Demo Company 073</t>
+  </si>
+  <si>
+    <t>Demo Company 074</t>
+  </si>
+  <si>
+    <t>Demo Company 075</t>
+  </si>
+  <si>
+    <t>Demo Company 076</t>
+  </si>
+  <si>
+    <t>Demo Company 077</t>
+  </si>
+  <si>
+    <t>Demo Company 078</t>
+  </si>
+  <si>
+    <t>Demo Company 079</t>
+  </si>
+  <si>
+    <t>Demo Company 080</t>
+  </si>
+  <si>
+    <t>Demo Company 081</t>
+  </si>
+  <si>
+    <t>Demo Company 082</t>
+  </si>
+  <si>
+    <t>Demo Company 083</t>
+  </si>
+  <si>
+    <t>Demo Company 084</t>
+  </si>
+  <si>
+    <t>Demo Company 085</t>
+  </si>
+  <si>
+    <t>Demo Company 086</t>
+  </si>
+  <si>
+    <t>Demo Company 087</t>
+  </si>
+  <si>
+    <t>Demo Company 088</t>
+  </si>
+  <si>
+    <t>Demo Company 089</t>
+  </si>
+  <si>
+    <t>Demo Company 090</t>
+  </si>
+  <si>
+    <t>Demo Company 091</t>
+  </si>
+  <si>
+    <t>Demo Company 092</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Consumer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,13 +620,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -130,22 +654,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -438,10 +956,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,73 +978,2400 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>192</v>
+      </c>
+      <c r="E2">
+        <v>101</v>
+      </c>
+      <c r="F2">
+        <v>152</v>
+      </c>
+      <c r="G2">
+        <v>36.6058394160584</v>
+      </c>
+      <c r="H2">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>192</v>
+      </c>
+      <c r="E3">
+        <v>102</v>
+      </c>
+      <c r="F3">
+        <v>154</v>
+      </c>
+      <c r="G3">
+        <v>999</v>
+      </c>
+      <c r="H3">
+        <v>25.39255813953489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4">
+        <v>103</v>
+      </c>
+      <c r="F4">
+        <v>156</v>
+      </c>
+      <c r="G4">
+        <v>37.90590809628009</v>
+      </c>
+      <c r="H4">
+        <v>28.45564841498559</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5">
+        <v>104</v>
+      </c>
+      <c r="F5">
+        <v>158</v>
+      </c>
+      <c r="G5">
+        <v>38.5125</v>
+      </c>
+      <c r="H5">
+        <v>31.69028571428571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6">
+        <v>105</v>
+      </c>
+      <c r="F6">
+        <v>160</v>
+      </c>
+      <c r="G6">
+        <v>39.09542743538768</v>
+      </c>
+      <c r="H6">
+        <v>26.7399433427762</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <v>162</v>
+      </c>
+      <c r="G7">
+        <v>39.65779467680609</v>
+      </c>
+      <c r="H7">
+        <v>29.88370786516854</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8">
+        <v>107</v>
+      </c>
+      <c r="F8">
+        <v>164</v>
+      </c>
+      <c r="G8">
+        <v>26.80145719489982</v>
+      </c>
+      <c r="H8">
+        <v>22.1324791086351</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>166</v>
+      </c>
+      <c r="G9">
+        <v>27.77097902097903</v>
+      </c>
+      <c r="H9">
+        <v>25.01229281767956</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10">
+        <v>109</v>
+      </c>
+      <c r="F10">
+        <v>168</v>
+      </c>
+      <c r="G10">
+        <v>28.69243697478991</v>
+      </c>
+      <c r="H10">
+        <v>28.06356164383562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11">
+        <v>110</v>
+      </c>
+      <c r="F11">
+        <v>170</v>
+      </c>
+      <c r="G11">
+        <v>43.7200956937799</v>
+      </c>
+      <c r="H11">
+        <v>23.83695652173913</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12">
+        <v>111</v>
+      </c>
+      <c r="F12">
+        <v>172</v>
+      </c>
+      <c r="G12">
+        <v>44.20408163265307</v>
+      </c>
+      <c r="H12">
+        <v>26.79768194070081</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13">
+        <v>112</v>
+      </c>
+      <c r="F13">
+        <v>174</v>
+      </c>
+      <c r="G13">
+        <v>44.67456896551724</v>
+      </c>
+      <c r="H13">
+        <v>29.92957219251337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E14">
+        <v>113</v>
+      </c>
+      <c r="F14">
+        <v>176</v>
+      </c>
+      <c r="G14">
+        <v>58.30238726790451</v>
+      </c>
+      <c r="H14">
+        <v>33.23236074270557</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E15">
+        <v>114</v>
+      </c>
+      <c r="F15">
+        <v>178</v>
+      </c>
+      <c r="G15">
+        <v>30.38823529411765</v>
+      </c>
+      <c r="H15">
+        <v>24.47052631578948</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16">
+        <v>115</v>
+      </c>
+      <c r="F16">
+        <v>180</v>
+      </c>
+      <c r="G16">
+        <v>31.37898686679175</v>
+      </c>
+      <c r="H16">
+        <v>20.96083550913838</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17">
+        <v>116</v>
+      </c>
+      <c r="F17">
+        <v>182</v>
+      </c>
+      <c r="G17">
+        <v>32.31654676258993</v>
+      </c>
+      <c r="H17">
+        <v>23.74010362694301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" t="s">
+        <v>192</v>
+      </c>
+      <c r="E18">
+        <v>117</v>
+      </c>
+      <c r="F18">
+        <v>184</v>
+      </c>
+      <c r="G18">
+        <v>33.20725388601036</v>
+      </c>
+      <c r="H18">
+        <v>26.69043701799486</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19">
+        <v>118</v>
+      </c>
+      <c r="F19">
+        <v>186</v>
+      </c>
+      <c r="G19">
+        <v>34.05647840531562</v>
+      </c>
+      <c r="H19">
+        <v>29.81158163265306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" t="s">
+        <v>192</v>
+      </c>
+      <c r="E20">
+        <v>119</v>
+      </c>
+      <c r="F20">
+        <v>188</v>
+      </c>
+      <c r="G20">
+        <v>34.8688</v>
+      </c>
+      <c r="H20">
+        <v>33.10329113924051</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21">
+        <v>120</v>
+      </c>
+      <c r="F21">
+        <v>190</v>
+      </c>
+      <c r="G21">
+        <v>51.5625</v>
+      </c>
+      <c r="H21">
+        <v>27.85929648241206</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22">
+        <v>121</v>
+      </c>
+      <c r="F22">
+        <v>192</v>
+      </c>
+      <c r="G22">
+        <v>34.56900212314225</v>
+      </c>
+      <c r="H22">
+        <v>20.70778054862843</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23">
+        <v>122</v>
+      </c>
+      <c r="F23">
+        <v>194</v>
+      </c>
+      <c r="G23">
+        <v>35.55668016194333</v>
+      </c>
+      <c r="H23">
+        <v>23.47797029702971</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24">
+        <v>123</v>
+      </c>
+      <c r="F24">
+        <v>196</v>
+      </c>
+      <c r="G24">
+        <v>36.48742746615088</v>
+      </c>
+      <c r="H24">
+        <v>26.41886977886978</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25">
+        <v>124</v>
+      </c>
+      <c r="F25">
+        <v>198</v>
+      </c>
+      <c r="G25">
+        <v>37.36851851851852</v>
+      </c>
+      <c r="H25">
+        <v>29.53024390243903</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26">
+        <v>125</v>
+      </c>
+      <c r="F26">
+        <v>200</v>
+      </c>
+      <c r="G26">
+        <v>38.20603907637656</v>
+      </c>
+      <c r="H26">
+        <v>24.99951573849879</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27">
+        <v>126</v>
+      </c>
+      <c r="F27">
+        <v>202</v>
+      </c>
+      <c r="G27">
+        <v>54.94471153846153</v>
+      </c>
+      <c r="H27">
+        <v>28.02180288461539</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28">
+        <v>127</v>
+      </c>
+      <c r="F28">
+        <v>204</v>
+      </c>
+      <c r="G28">
+        <v>39.77011494252874</v>
+      </c>
+      <c r="H28">
+        <v>31.21431980906921</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29">
+        <v>128</v>
+      </c>
+      <c r="F29">
+        <v>206</v>
+      </c>
+      <c r="G29">
+        <v>27.00316455696203</v>
+      </c>
+      <c r="H29">
+        <v>23.05123222748815</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30">
+        <v>129</v>
+      </c>
+      <c r="F30">
+        <v>208</v>
+      </c>
+      <c r="G30">
+        <v>28.09923664122138</v>
+      </c>
+      <c r="H30">
+        <v>25.98352941176471</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31">
+        <v>130</v>
+      </c>
+      <c r="F31">
+        <v>210</v>
+      </c>
+      <c r="G31">
+        <v>41.33891213389121</v>
+      </c>
+      <c r="H31">
+        <v>22.1607476635514</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32">
+        <v>131</v>
+      </c>
+      <c r="F32">
+        <v>212</v>
+      </c>
+      <c r="G32">
+        <v>42.17764471057885</v>
+      </c>
+      <c r="H32">
+        <v>25.00419953596288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E33">
+        <v>132</v>
+      </c>
+      <c r="F33">
+        <v>214</v>
+      </c>
+      <c r="G33">
+        <v>42.9732824427481</v>
+      </c>
+      <c r="H33">
+        <v>28.01778801843319</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34">
+        <v>133</v>
+      </c>
+      <c r="F34">
+        <v>216</v>
+      </c>
+      <c r="G34">
+        <v>43.73126142595979</v>
+      </c>
+      <c r="H34">
+        <v>31.20130434782608</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35">
+        <v>134</v>
+      </c>
+      <c r="F35">
+        <v>218</v>
+      </c>
+      <c r="G35">
+        <v>44.45614035087719</v>
+      </c>
+      <c r="H35">
+        <v>34.55454545454545</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36">
+        <v>135</v>
+      </c>
+      <c r="F36">
+        <v>220</v>
+      </c>
+      <c r="G36">
+        <v>30.10118043844857</v>
+      </c>
+      <c r="H36">
+        <v>19.34085778781039</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D37" t="s">
+        <v>194</v>
+      </c>
+      <c r="E37">
+        <v>136</v>
+      </c>
+      <c r="F37">
+        <v>222</v>
+      </c>
+      <c r="G37">
+        <v>31.24188311688312</v>
+      </c>
+      <c r="H37">
+        <v>22.00661434977579</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38">
+        <v>137</v>
+      </c>
+      <c r="F38">
+        <v>224</v>
+      </c>
+      <c r="G38">
+        <v>32.32550860719875</v>
+      </c>
+      <c r="H38">
+        <v>24.84240534521158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39">
+        <v>138</v>
+      </c>
+      <c r="F39">
+        <v>226</v>
+      </c>
+      <c r="G39">
+        <v>33.35800604229608</v>
+      </c>
+      <c r="H39">
+        <v>27.84803097345133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40">
+        <v>139</v>
+      </c>
+      <c r="F40">
+        <v>228</v>
+      </c>
+      <c r="G40">
+        <v>51.70549450549451</v>
+      </c>
+      <c r="H40">
+        <v>31.0232967032967</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" t="s">
+        <v>194</v>
+      </c>
+      <c r="E41">
+        <v>140</v>
+      </c>
+      <c r="F41">
+        <v>230</v>
+      </c>
+      <c r="G41">
+        <v>49.18307086614173</v>
+      </c>
+      <c r="H41">
+        <v>26.18515283842795</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42">
+        <v>141</v>
+      </c>
+      <c r="F42">
+        <v>232</v>
+      </c>
+      <c r="G42">
+        <v>49.83050847457628</v>
+      </c>
+      <c r="H42">
+        <v>29.27245119305858</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43">
+        <v>142</v>
+      </c>
+      <c r="F43">
+        <v>234</v>
+      </c>
+      <c r="G43">
+        <v>33.63537906137184</v>
+      </c>
+      <c r="H43">
+        <v>21.68612068965518</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>142</v>
+      </c>
+      <c r="D44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44">
+        <v>143</v>
+      </c>
+      <c r="F44">
+        <v>236</v>
+      </c>
+      <c r="G44">
+        <v>34.80935875216638</v>
+      </c>
+      <c r="H44">
+        <v>24.51488222698073</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" t="s">
+        <v>194</v>
+      </c>
+      <c r="E45">
+        <v>144</v>
+      </c>
+      <c r="F45">
+        <v>238</v>
+      </c>
+      <c r="G45">
+        <v>35.92</v>
+      </c>
+      <c r="H45">
+        <v>27.51319148936171</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" t="s">
+        <v>194</v>
+      </c>
+      <c r="E46">
+        <v>145</v>
+      </c>
+      <c r="F46">
+        <v>240</v>
+      </c>
+      <c r="G46">
+        <v>36.97431781701445</v>
+      </c>
+      <c r="H46">
+        <v>23.37589852008457</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
+        <v>145</v>
+      </c>
+      <c r="D47" t="s">
+        <v>194</v>
+      </c>
+      <c r="E47">
+        <v>146</v>
+      </c>
+      <c r="F47">
+        <v>242</v>
+      </c>
+      <c r="G47">
+        <v>37.97832817337462</v>
+      </c>
+      <c r="H47">
+        <v>26.28642857142858</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" t="s">
+        <v>194</v>
+      </c>
+      <c r="E48">
+        <v>147</v>
+      </c>
+      <c r="F48">
+        <v>244</v>
+      </c>
+      <c r="G48">
+        <v>38.93721973094171</v>
+      </c>
+      <c r="H48">
+        <v>29.36630480167015</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49">
+        <v>148</v>
+      </c>
+      <c r="F49">
+        <v>246</v>
+      </c>
+      <c r="G49">
+        <v>39.85549132947977</v>
+      </c>
+      <c r="H49">
+        <v>32.61535269709543</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" t="s">
+        <v>194</v>
+      </c>
+      <c r="E50">
+        <v>149</v>
+      </c>
+      <c r="F50">
+        <v>248</v>
+      </c>
+      <c r="G50">
+        <v>27.15804195804196</v>
+      </c>
+      <c r="H50">
+        <v>24.02226804123711</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51">
+        <v>150</v>
+      </c>
+      <c r="F51">
+        <v>250</v>
+      </c>
+      <c r="G51">
+        <v>38.89405204460967</v>
+      </c>
+      <c r="H51">
+        <v>20.58196721311476</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" t="s">
+        <v>194</v>
+      </c>
+      <c r="E52">
+        <v>151</v>
+      </c>
+      <c r="F52">
+        <v>252</v>
+      </c>
+      <c r="G52">
+        <v>40.01426024955438</v>
+      </c>
+      <c r="H52">
+        <v>23.31665987780041</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D53" t="s">
+        <v>194</v>
+      </c>
+      <c r="E53">
+        <v>152</v>
+      </c>
+      <c r="F53">
+        <v>254</v>
+      </c>
+      <c r="G53">
+        <v>48.55668016194332</v>
+      </c>
+      <c r="H53">
+        <v>26.2206072874494</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54">
+        <v>153</v>
+      </c>
+      <c r="F54">
+        <v>256</v>
+      </c>
+      <c r="G54">
+        <v>42.07907742998353</v>
+      </c>
+      <c r="H54">
+        <v>29.29364185110664</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55">
+        <v>154</v>
+      </c>
+      <c r="F55">
+        <v>258</v>
+      </c>
+      <c r="G55">
+        <v>43.03650793650793</v>
+      </c>
+      <c r="H55">
+        <v>32.5356</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>154</v>
+      </c>
+      <c r="D56" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56">
+        <v>155</v>
+      </c>
+      <c r="F56">
+        <v>260</v>
+      </c>
+      <c r="G56">
+        <v>43.95099540581929</v>
+      </c>
+      <c r="H56">
+        <v>27.38767395626243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57">
+        <v>156</v>
+      </c>
+      <c r="F57">
+        <v>262</v>
+      </c>
+      <c r="G57">
+        <v>29.88461538461539</v>
+      </c>
+      <c r="H57">
+        <v>20.36169960474308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" t="s">
+        <v>194</v>
+      </c>
+      <c r="E58">
+        <v>157</v>
+      </c>
+      <c r="F58">
+        <v>264</v>
+      </c>
+      <c r="G58">
+        <v>31.13733905579399</v>
+      </c>
+      <c r="H58">
+        <v>23.09056974459725</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" t="s">
+        <v>194</v>
+      </c>
+      <c r="E59">
+        <v>158</v>
+      </c>
+      <c r="F59">
+        <v>266</v>
+      </c>
+      <c r="G59">
+        <v>32.33240997229917</v>
+      </c>
+      <c r="H59">
+        <v>25.9884375</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" t="s">
+        <v>194</v>
+      </c>
+      <c r="E60">
+        <v>159</v>
+      </c>
+      <c r="F60">
+        <v>268</v>
+      </c>
+      <c r="G60">
+        <v>33.4751677852349</v>
+      </c>
+      <c r="H60">
+        <v>29.05514563106796</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61">
+        <v>160</v>
+      </c>
+      <c r="F61">
+        <v>270</v>
+      </c>
+      <c r="G61">
+        <v>46.74295774647889</v>
+      </c>
+      <c r="H61">
+        <v>24.60231660231661</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" t="s">
+        <v>194</v>
+      </c>
+      <c r="E62">
+        <v>161</v>
+      </c>
+      <c r="F62">
+        <v>272</v>
+      </c>
+      <c r="G62">
+        <v>47.67681895093062</v>
+      </c>
+      <c r="H62">
+        <v>27.58209213051823</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63">
+        <v>162</v>
+      </c>
+      <c r="F63">
+        <v>274</v>
+      </c>
+      <c r="G63">
+        <v>48.56677524429967</v>
+      </c>
+      <c r="H63">
+        <v>30.73053435114504</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" t="s">
+        <v>194</v>
+      </c>
+      <c r="E64">
+        <v>163</v>
+      </c>
+      <c r="F64">
+        <v>276</v>
+      </c>
+      <c r="G64">
+        <v>32.94505494505495</v>
+      </c>
+      <c r="H64">
+        <v>22.69833017077799</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" t="s">
+        <v>163</v>
+      </c>
+      <c r="D65" t="s">
+        <v>194</v>
+      </c>
+      <c r="E65">
+        <v>164</v>
+      </c>
+      <c r="F65">
+        <v>278</v>
+      </c>
+      <c r="G65">
+        <v>34.25000000000001</v>
+      </c>
+      <c r="H65">
+        <v>25.59056603773585</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" t="s">
+        <v>164</v>
+      </c>
+      <c r="D66" t="s">
+        <v>194</v>
+      </c>
+      <c r="E66">
+        <v>165</v>
+      </c>
+      <c r="F66">
+        <v>280</v>
+      </c>
+      <c r="G66">
+        <v>45.47842401500938</v>
+      </c>
+      <c r="H66">
+        <v>21.8296435272045</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" t="s">
+        <v>194</v>
+      </c>
+      <c r="E67">
+        <v>166</v>
+      </c>
+      <c r="F67">
+        <v>282</v>
+      </c>
+      <c r="G67">
+        <v>36.67280453257791</v>
+      </c>
+      <c r="H67">
+        <v>24.63509328358209</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>166</v>
+      </c>
+      <c r="D68" t="s">
+        <v>194</v>
+      </c>
+      <c r="E68">
+        <v>167</v>
+      </c>
+      <c r="F68">
+        <v>284</v>
+      </c>
+      <c r="G68">
+        <v>37.80246913580248</v>
+      </c>
+      <c r="H68">
+        <v>27.60912801484231</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" t="s">
+        <v>194</v>
+      </c>
+      <c r="E69">
+        <v>168</v>
+      </c>
+      <c r="F69">
+        <v>286</v>
+      </c>
+      <c r="G69">
+        <v>38.8843085106383</v>
+      </c>
+      <c r="H69">
+        <v>30.75160516605166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70">
+        <v>169</v>
+      </c>
+      <c r="F70">
+        <v>288</v>
+      </c>
+      <c r="G70">
+        <v>39.92258064516129</v>
+      </c>
+      <c r="H70">
+        <v>34.06238532110092</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" t="s">
+        <v>169</v>
+      </c>
+      <c r="D71" t="s">
+        <v>194</v>
+      </c>
+      <c r="E71">
+        <v>170</v>
+      </c>
+      <c r="F71">
+        <v>290</v>
+      </c>
+      <c r="G71">
+        <v>36.4046822742475</v>
+      </c>
+      <c r="H71">
+        <v>19.06861313868613</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" t="s">
+        <v>170</v>
+      </c>
+      <c r="D72" t="s">
+        <v>194</v>
+      </c>
+      <c r="E72">
+        <v>171</v>
+      </c>
+      <c r="F72">
+        <v>292</v>
+      </c>
+      <c r="G72">
+        <v>37.7536231884058</v>
+      </c>
+      <c r="H72">
+        <v>21.70045372050817</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D73" t="s">
+        <v>194</v>
+      </c>
+      <c r="E73">
+        <v>172</v>
+      </c>
+      <c r="F73">
+        <v>294</v>
+      </c>
+      <c r="G73">
+        <v>39.03105590062112</v>
+      </c>
+      <c r="H73">
+        <v>24.50079422382672</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" t="s">
+        <v>194</v>
+      </c>
+      <c r="E74">
+        <v>173</v>
+      </c>
+      <c r="F74">
+        <v>296</v>
+      </c>
+      <c r="G74">
+        <v>40.24437781109446</v>
+      </c>
+      <c r="H74">
+        <v>27.4694973070018</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" t="s">
+        <v>194</v>
+      </c>
+      <c r="E75">
+        <v>174</v>
+      </c>
+      <c r="F75">
+        <v>298</v>
+      </c>
+      <c r="G75">
+        <v>41.40000000000001</v>
+      </c>
+      <c r="H75">
+        <v>30.60642857142857</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" t="s">
+        <v>174</v>
+      </c>
+      <c r="D76" t="s">
+        <v>194</v>
+      </c>
+      <c r="E76">
+        <v>175</v>
+      </c>
+      <c r="F76">
+        <v>300</v>
+      </c>
+      <c r="G76">
+        <v>42.50350631136045</v>
+      </c>
+      <c r="H76">
+        <v>25.83730017761989</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
+        <v>175</v>
+      </c>
+      <c r="D77" t="s">
+        <v>194</v>
+      </c>
+      <c r="E77">
+        <v>176</v>
+      </c>
+      <c r="F77">
+        <v>302</v>
+      </c>
+      <c r="G77">
+        <v>43.55978260869566</v>
+      </c>
+      <c r="H77">
+        <v>28.88798586572439</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" t="s">
+        <v>176</v>
+      </c>
+      <c r="D78" t="s">
+        <v>194</v>
+      </c>
+      <c r="E78">
+        <v>177</v>
+      </c>
+      <c r="F78">
+        <v>304</v>
+      </c>
+      <c r="G78">
+        <v>29.71541501976285</v>
+      </c>
+      <c r="H78">
+        <v>21.40449912126538</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" t="s">
+        <v>177</v>
+      </c>
+      <c r="D79" t="s">
+        <v>194</v>
+      </c>
+      <c r="E79">
+        <v>178</v>
+      </c>
+      <c r="F79">
+        <v>306</v>
+      </c>
+      <c r="G79">
+        <v>42.45629370629371</v>
+      </c>
+      <c r="H79">
+        <v>24.20008741258741</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" t="s">
+        <v>178</v>
+      </c>
+      <c r="D80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E80">
+        <v>179</v>
+      </c>
+      <c r="F80">
+        <v>308</v>
+      </c>
+      <c r="G80">
+        <v>32.33788819875777</v>
+      </c>
+      <c r="H80">
+        <v>27.16382608695652</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" t="s">
+        <v>194</v>
+      </c>
+      <c r="E81">
+        <v>180</v>
+      </c>
+      <c r="F81">
+        <v>310</v>
+      </c>
+      <c r="G81">
+        <v>44.25955414012739</v>
+      </c>
+      <c r="H81">
+        <v>23.08235294117648</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" t="s">
+        <v>180</v>
+      </c>
+      <c r="D82" t="s">
+        <v>194</v>
+      </c>
+      <c r="E82">
+        <v>181</v>
+      </c>
+      <c r="F82">
+        <v>312</v>
+      </c>
+      <c r="G82">
+        <v>45.42857142857143</v>
+      </c>
+      <c r="H82">
+        <v>25.95996557659209</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" t="s">
+        <v>194</v>
+      </c>
+      <c r="E83">
+        <v>182</v>
+      </c>
+      <c r="F83">
+        <v>314</v>
+      </c>
+      <c r="G83">
+        <v>46.54154302670624</v>
+      </c>
+      <c r="H83">
+        <v>29.00558219178083</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>90</v>
+      </c>
+      <c r="C84" t="s">
+        <v>182</v>
+      </c>
+      <c r="D84" t="s">
+        <v>194</v>
+      </c>
+      <c r="E84">
+        <v>183</v>
+      </c>
+      <c r="F84">
+        <v>316</v>
+      </c>
+      <c r="G84">
+        <v>47.60401721664276</v>
+      </c>
+      <c r="H84">
+        <v>32.2190800681431</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" t="s">
+        <v>183</v>
+      </c>
+      <c r="D85" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85">
+        <v>184</v>
+      </c>
+      <c r="F85">
+        <v>318</v>
+      </c>
+      <c r="G85">
+        <v>32.41388888888889</v>
+      </c>
+      <c r="H85">
+        <v>23.7335593220339</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86" t="s">
+        <v>184</v>
+      </c>
+      <c r="D86" t="s">
+        <v>194</v>
+      </c>
+      <c r="E86">
+        <v>185</v>
+      </c>
+      <c r="F86">
+        <v>320</v>
+      </c>
+      <c r="G86">
+        <v>33.81561238223419</v>
+      </c>
+      <c r="H86">
+        <v>20.33726812816189</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" t="s">
+        <v>185</v>
+      </c>
+      <c r="D87" t="s">
+        <v>194</v>
+      </c>
+      <c r="E87">
+        <v>186</v>
+      </c>
+      <c r="F87">
+        <v>322</v>
+      </c>
+      <c r="G87">
+        <v>35.15404699738904</v>
+      </c>
+      <c r="H87">
+        <v>23.04241610738255</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" t="s">
+        <v>194</v>
+      </c>
+      <c r="E88">
+        <v>187</v>
+      </c>
+      <c r="F88">
+        <v>324</v>
+      </c>
+      <c r="G88">
+        <v>36.43472750316857</v>
+      </c>
+      <c r="H88">
+        <v>25.91549248747913</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" t="s">
+        <v>194</v>
+      </c>
+      <c r="E89">
+        <v>188</v>
+      </c>
+      <c r="F89">
+        <v>326</v>
+      </c>
+      <c r="G89">
+        <v>168.9613259668508</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>96</v>
+      </c>
+      <c r="C90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D90" t="s">
+        <v>194</v>
+      </c>
+      <c r="E90">
+        <v>189</v>
+      </c>
+      <c r="F90">
+        <v>328</v>
+      </c>
+      <c r="G90">
+        <v>160.559405940594</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>97</v>
+      </c>
+      <c r="C91" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91">
+        <v>190</v>
+      </c>
+      <c r="F91">
+        <v>330</v>
+      </c>
+      <c r="G91">
+        <v>52.12765957446809</v>
+      </c>
+      <c r="H91">
+        <v>27.07894736842105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92" t="s">
+        <v>190</v>
+      </c>
+      <c r="D92" t="s">
+        <v>194</v>
+      </c>
+      <c r="E92">
+        <v>191</v>
+      </c>
+      <c r="F92">
+        <v>332</v>
+      </c>
+      <c r="G92">
+        <v>39.47954173486089</v>
+      </c>
+      <c r="H92">
+        <v>20.13456628477905</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D93" t="s">
+        <v>194</v>
+      </c>
+      <c r="E93">
+        <v>192</v>
+      </c>
+      <c r="F93">
+        <v>334</v>
+      </c>
+      <c r="G93">
+        <v>36.88210227272728</v>
+      </c>
+      <c r="H93">
+        <v>22.835667752443</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>